--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3956,6 +3956,235 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125320133</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Melen, Melen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>410826</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7022809</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125320300</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Melen, Melen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>410844</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7022833</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -3958,10 +3958,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125320133</v>
+        <v>125320300</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3974,39 +3974,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Melen, Melen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410826</v>
+        <v>410844</v>
       </c>
       <c r="R34" t="n">
-        <v>7022809</v>
+        <v>7022833</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,7 +4033,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4048,7 +4043,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4075,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125320300</v>
+        <v>125320133</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4091,34 +4086,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Melen, Melen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410844</v>
+        <v>410826</v>
       </c>
       <c r="R35" t="n">
-        <v>7022833</v>
+        <v>7022809</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4150,7 +4153,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4160,7 +4163,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -3961,7 +3961,7 @@
         <v>125320300</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>125320133</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -3961,12 +3961,7 @@
         <v>125320300</v>
       </c>
       <c r="B34" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4073,12 +4068,7 @@
         <v>125320133</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -3961,7 +3961,7 @@
         <v>125320300</v>
       </c>
       <c r="B34" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -3961,7 +3961,7 @@
         <v>125320300</v>
       </c>
       <c r="B34" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -3961,7 +3961,7 @@
         <v>125320300</v>
       </c>
       <c r="B34" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -4068,7 +4068,7 @@
         <v>125320133</v>
       </c>
       <c r="B35" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -4068,7 +4068,7 @@
         <v>125320133</v>
       </c>
       <c r="B35" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 15145-2025 artfynd.xlsx
+++ b/artfynd/A 15145-2025 artfynd.xlsx
@@ -4068,7 +4068,7 @@
         <v>125320133</v>
       </c>
       <c r="B35" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
